--- a/VerveStacks_NGA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NGA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98EF0FA1-FB14-43B0-AD8A-A809D19DB5C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3BFCCC4-3545-403C-AD48-5AA31B2D70BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="424">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -618,6 +618,9 @@
     <t>wnid offshore potential</t>
   </si>
   <si>
+    <t>ELC_BatIn</t>
+  </si>
+  <si>
     <t>~fi_process</t>
   </si>
   <si>
@@ -1393,6 +1396,9 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</t>
   </si>
 </sst>
 </file>
@@ -3286,7 +3292,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3308,7 +3314,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3323,7 +3329,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>19</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -4800,9 +4806,8 @@
     <row r="8" spans="2:25" ht="17.649999999999999">
       <c r="B8" s="20"/>
       <c r="E8" s="26"/>
-      <c r="F8" t="str">
-        <f>C5</f>
-        <v>ELC</v>
+      <c r="F8" t="s">
+        <v>163</v>
       </c>
       <c r="G8" t="str">
         <f>E7</f>
@@ -6125,80 +6130,80 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E5AAF78-D3C9-4E28-A1D2-0AF2E076C17E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB216AA-CDC8-4C85-B4F7-86F06E14C449}">
   <dimension ref="B9:M46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:13">
       <c r="B9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J10" t="s">
         <v>166</v>
       </c>
-      <c r="E10" t="s">
-        <v>167</v>
-      </c>
-      <c r="F10" t="s">
-        <v>168</v>
-      </c>
-      <c r="G10" t="s">
-        <v>169</v>
-      </c>
-      <c r="H10" t="s">
-        <v>170</v>
-      </c>
-      <c r="J10" t="s">
-        <v>165</v>
-      </c>
       <c r="K10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" t="s">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J11" t="s">
         <v>173</v>
       </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" t="s">
-        <v>174</v>
-      </c>
-      <c r="H11" t="s">
-        <v>175</v>
-      </c>
-      <c r="J11" t="s">
-        <v>172</v>
-      </c>
       <c r="K11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L11">
         <v>7.4014265365578122</v>
@@ -6209,31 +6214,31 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" t="s">
+        <v>175</v>
+      </c>
+      <c r="H12" t="s">
         <v>176</v>
       </c>
-      <c r="D12" t="s">
+      <c r="J12" t="s">
         <v>177</v>
       </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" t="s">
-        <v>174</v>
-      </c>
-      <c r="H12" t="s">
-        <v>175</v>
-      </c>
-      <c r="J12" t="s">
-        <v>176</v>
-      </c>
       <c r="K12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L12">
         <v>7.3012581452158205</v>
@@ -6244,31 +6249,31 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D13" t="s">
+        <v>180</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>175</v>
+      </c>
+      <c r="H13" t="s">
+        <v>176</v>
+      </c>
+      <c r="J13" t="s">
         <v>179</v>
       </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" t="s">
-        <v>174</v>
-      </c>
-      <c r="H13" t="s">
-        <v>175</v>
-      </c>
-      <c r="J13" t="s">
-        <v>178</v>
-      </c>
       <c r="K13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L13">
         <v>6.3569135279785387</v>
@@ -6279,31 +6284,31 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D14" t="s">
+        <v>182</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" t="s">
+        <v>176</v>
+      </c>
+      <c r="J14" t="s">
         <v>181</v>
       </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" t="s">
-        <v>174</v>
-      </c>
-      <c r="H14" t="s">
-        <v>175</v>
-      </c>
-      <c r="J14" t="s">
-        <v>180</v>
-      </c>
       <c r="K14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L14">
         <v>8.7076103908487088</v>
@@ -6314,31 +6319,31 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>176</v>
+      </c>
+      <c r="J15" t="s">
         <v>183</v>
       </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" t="s">
-        <v>174</v>
-      </c>
-      <c r="H15" t="s">
-        <v>175</v>
-      </c>
-      <c r="J15" t="s">
-        <v>182</v>
-      </c>
       <c r="K15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L15">
         <v>9.6059669790949886</v>
@@ -6349,31 +6354,31 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H16" t="s">
+        <v>176</v>
+      </c>
+      <c r="J16" t="s">
         <v>185</v>
       </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" t="s">
-        <v>174</v>
-      </c>
-      <c r="H16" t="s">
-        <v>175</v>
-      </c>
-      <c r="J16" t="s">
-        <v>184</v>
-      </c>
       <c r="K16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L16">
         <v>1.494</v>
@@ -6384,31 +6389,31 @@
     </row>
     <row r="17" spans="2:13">
       <c r="B17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>176</v>
+      </c>
+      <c r="J17" t="s">
         <v>187</v>
       </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" t="s">
-        <v>174</v>
-      </c>
-      <c r="H17" t="s">
-        <v>175</v>
-      </c>
-      <c r="J17" t="s">
-        <v>186</v>
-      </c>
       <c r="K17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L17">
         <v>0.73950000000000005</v>
@@ -6419,31 +6424,31 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" t="s">
+        <v>175</v>
+      </c>
+      <c r="H18" t="s">
+        <v>176</v>
+      </c>
+      <c r="J18" t="s">
         <v>189</v>
       </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" t="s">
-        <v>174</v>
-      </c>
-      <c r="H18" t="s">
-        <v>175</v>
-      </c>
-      <c r="J18" t="s">
-        <v>188</v>
-      </c>
       <c r="K18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L18">
         <v>6.42225</v>
@@ -6454,31 +6459,31 @@
     </row>
     <row r="19" spans="2:13">
       <c r="B19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>176</v>
+      </c>
+      <c r="J19" t="s">
         <v>191</v>
       </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" t="s">
-        <v>174</v>
-      </c>
-      <c r="H19" t="s">
-        <v>175</v>
-      </c>
-      <c r="J19" t="s">
-        <v>190</v>
-      </c>
       <c r="K19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L19">
         <v>0.77475000000000005</v>
@@ -6489,31 +6494,31 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D20" t="s">
+        <v>194</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" t="s">
+        <v>175</v>
+      </c>
+      <c r="H20" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" t="s">
         <v>193</v>
       </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" t="s">
-        <v>174</v>
-      </c>
-      <c r="H20" t="s">
-        <v>175</v>
-      </c>
-      <c r="J20" t="s">
-        <v>192</v>
-      </c>
       <c r="K20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L20">
         <v>7.9035000000000002</v>
@@ -6524,31 +6529,31 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D21" t="s">
+        <v>196</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" t="s">
+        <v>175</v>
+      </c>
+      <c r="H21" t="s">
+        <v>176</v>
+      </c>
+      <c r="J21" t="s">
         <v>195</v>
       </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" t="s">
-        <v>174</v>
-      </c>
-      <c r="H21" t="s">
-        <v>175</v>
-      </c>
-      <c r="J21" t="s">
-        <v>194</v>
-      </c>
       <c r="K21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L21">
         <v>6.856025730657799</v>
@@ -6559,31 +6564,31 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D22" t="s">
+        <v>198</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" t="s">
+        <v>175</v>
+      </c>
+      <c r="H22" t="s">
+        <v>176</v>
+      </c>
+      <c r="J22" t="s">
         <v>197</v>
       </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" t="s">
-        <v>174</v>
-      </c>
-      <c r="H22" t="s">
-        <v>175</v>
-      </c>
-      <c r="J22" t="s">
-        <v>196</v>
-      </c>
       <c r="K22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L22">
         <v>1.3986753229694648</v>
@@ -6594,31 +6599,31 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D23" t="s">
+        <v>200</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" t="s">
+        <v>176</v>
+      </c>
+      <c r="J23" t="s">
         <v>199</v>
       </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" t="s">
-        <v>174</v>
-      </c>
-      <c r="H23" t="s">
-        <v>175</v>
-      </c>
-      <c r="J23" t="s">
-        <v>198</v>
-      </c>
       <c r="K23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L23">
         <v>3.4612850521844623</v>
@@ -6629,31 +6634,31 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D24" t="s">
+        <v>202</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" t="s">
+        <v>175</v>
+      </c>
+      <c r="H24" t="s">
+        <v>176</v>
+      </c>
+      <c r="J24" t="s">
         <v>201</v>
       </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" t="s">
-        <v>174</v>
-      </c>
-      <c r="H24" t="s">
-        <v>175</v>
-      </c>
-      <c r="J24" t="s">
-        <v>200</v>
-      </c>
       <c r="K24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L24">
         <v>1.8124828097378689</v>
@@ -6664,31 +6669,31 @@
     </row>
     <row r="25" spans="2:13">
       <c r="B25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D25" t="s">
+        <v>204</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>175</v>
+      </c>
+      <c r="H25" t="s">
+        <v>176</v>
+      </c>
+      <c r="J25" t="s">
         <v>203</v>
       </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" t="s">
-        <v>174</v>
-      </c>
-      <c r="H25" t="s">
-        <v>175</v>
-      </c>
-      <c r="J25" t="s">
-        <v>202</v>
-      </c>
       <c r="K25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L25">
         <v>0.19125</v>
@@ -6699,31 +6704,31 @@
     </row>
     <row r="26" spans="2:13">
       <c r="B26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>175</v>
+      </c>
+      <c r="H26" t="s">
+        <v>176</v>
+      </c>
+      <c r="J26" t="s">
         <v>205</v>
       </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" t="s">
-        <v>174</v>
-      </c>
-      <c r="H26" t="s">
-        <v>175</v>
-      </c>
-      <c r="J26" t="s">
-        <v>204</v>
-      </c>
       <c r="K26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L26">
         <v>23.243227098334987</v>
@@ -6734,31 +6739,31 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D27" t="s">
+        <v>208</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" t="s">
+        <v>175</v>
+      </c>
+      <c r="H27" t="s">
+        <v>176</v>
+      </c>
+      <c r="J27" t="s">
         <v>207</v>
       </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" t="s">
-        <v>174</v>
-      </c>
-      <c r="H27" t="s">
-        <v>175</v>
-      </c>
-      <c r="J27" t="s">
-        <v>206</v>
-      </c>
       <c r="K27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L27">
         <v>35.220837926026014</v>
@@ -6769,31 +6774,31 @@
     </row>
     <row r="28" spans="2:13">
       <c r="B28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D28" t="s">
+        <v>210</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>175</v>
+      </c>
+      <c r="H28" t="s">
+        <v>176</v>
+      </c>
+      <c r="J28" t="s">
         <v>209</v>
       </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" t="s">
-        <v>174</v>
-      </c>
-      <c r="H28" t="s">
-        <v>175</v>
-      </c>
-      <c r="J28" t="s">
-        <v>208</v>
-      </c>
       <c r="K28" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L28">
         <v>47.200072372633244</v>
@@ -6804,31 +6809,31 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D29" t="s">
+        <v>212</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" t="s">
+        <v>175</v>
+      </c>
+      <c r="H29" t="s">
+        <v>176</v>
+      </c>
+      <c r="J29" t="s">
         <v>211</v>
       </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" t="s">
-        <v>174</v>
-      </c>
-      <c r="H29" t="s">
-        <v>175</v>
-      </c>
-      <c r="J29" t="s">
-        <v>210</v>
-      </c>
       <c r="K29" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L29">
         <v>0.38250000000000001</v>
@@ -6839,31 +6844,31 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" t="s">
+        <v>175</v>
+      </c>
+      <c r="H30" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" t="s">
         <v>213</v>
       </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" t="s">
-        <v>174</v>
-      </c>
-      <c r="H30" t="s">
-        <v>175</v>
-      </c>
-      <c r="J30" t="s">
-        <v>212</v>
-      </c>
       <c r="K30" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L30">
         <v>2.7203951076717159</v>
@@ -6874,31 +6879,31 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D31" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" t="s">
+        <v>175</v>
+      </c>
+      <c r="H31" t="s">
+        <v>176</v>
+      </c>
+      <c r="J31" t="s">
         <v>215</v>
       </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" t="s">
-        <v>174</v>
-      </c>
-      <c r="H31" t="s">
-        <v>175</v>
-      </c>
-      <c r="J31" t="s">
-        <v>214</v>
-      </c>
       <c r="K31" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L31">
         <v>5.0946983462815121</v>
@@ -6909,31 +6914,31 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C32" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D32" t="s">
+        <v>218</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" t="s">
+        <v>176</v>
+      </c>
+      <c r="J32" t="s">
         <v>217</v>
       </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" t="s">
-        <v>174</v>
-      </c>
-      <c r="H32" t="s">
-        <v>175</v>
-      </c>
-      <c r="J32" t="s">
-        <v>216</v>
-      </c>
       <c r="K32" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L32">
         <v>1.2929486279019178</v>
@@ -6944,31 +6949,31 @@
     </row>
     <row r="33" spans="2:13">
       <c r="B33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C33" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" t="s">
+        <v>175</v>
+      </c>
+      <c r="H33" t="s">
+        <v>176</v>
+      </c>
+      <c r="J33" t="s">
         <v>219</v>
       </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" t="s">
-        <v>174</v>
-      </c>
-      <c r="H33" t="s">
-        <v>175</v>
-      </c>
-      <c r="J33" t="s">
-        <v>218</v>
-      </c>
       <c r="K33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L33">
         <v>0.94090199998176838</v>
@@ -6979,31 +6984,31 @@
     </row>
     <row r="34" spans="2:13">
       <c r="B34" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C34" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D34" t="s">
+        <v>222</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" t="s">
+        <v>175</v>
+      </c>
+      <c r="H34" t="s">
+        <v>176</v>
+      </c>
+      <c r="J34" t="s">
         <v>221</v>
       </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" t="s">
-        <v>174</v>
-      </c>
-      <c r="H34" t="s">
-        <v>175</v>
-      </c>
-      <c r="J34" t="s">
-        <v>220</v>
-      </c>
       <c r="K34" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L34">
         <v>14.508925289494702</v>
@@ -7014,31 +7019,31 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D35" t="s">
+        <v>224</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" t="s">
+        <v>175</v>
+      </c>
+      <c r="H35" t="s">
+        <v>176</v>
+      </c>
+      <c r="J35" t="s">
         <v>223</v>
       </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" t="s">
-        <v>174</v>
-      </c>
-      <c r="H35" t="s">
-        <v>175</v>
-      </c>
-      <c r="J35" t="s">
-        <v>222</v>
-      </c>
       <c r="K35" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L35">
         <v>12.448123931589503</v>
@@ -7049,31 +7054,31 @@
     </row>
     <row r="36" spans="2:13">
       <c r="B36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D36" t="s">
+        <v>226</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" t="s">
+        <v>175</v>
+      </c>
+      <c r="H36" t="s">
+        <v>176</v>
+      </c>
+      <c r="J36" t="s">
         <v>225</v>
       </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36" t="s">
-        <v>174</v>
-      </c>
-      <c r="H36" t="s">
-        <v>175</v>
-      </c>
-      <c r="J36" t="s">
-        <v>224</v>
-      </c>
       <c r="K36" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L36">
         <v>13.443097459865598</v>
@@ -7084,31 +7089,31 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D37" t="s">
+        <v>228</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" t="s">
+        <v>175</v>
+      </c>
+      <c r="H37" t="s">
+        <v>176</v>
+      </c>
+      <c r="J37" t="s">
         <v>227</v>
       </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37" t="s">
-        <v>174</v>
-      </c>
-      <c r="H37" t="s">
-        <v>175</v>
-      </c>
-      <c r="J37" t="s">
-        <v>226</v>
-      </c>
       <c r="K37" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L37">
         <v>49.917645562896887</v>
@@ -7119,31 +7124,31 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C38" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D38" t="s">
+        <v>230</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" t="s">
+        <v>175</v>
+      </c>
+      <c r="H38" t="s">
+        <v>176</v>
+      </c>
+      <c r="J38" t="s">
         <v>229</v>
       </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38" t="s">
-        <v>174</v>
-      </c>
-      <c r="H38" t="s">
-        <v>175</v>
-      </c>
-      <c r="J38" t="s">
-        <v>228</v>
-      </c>
       <c r="K38" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L38">
         <v>16.338359943235197</v>
@@ -7154,31 +7159,31 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C39" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D39" t="s">
+        <v>232</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" t="s">
+        <v>175</v>
+      </c>
+      <c r="H39" t="s">
+        <v>176</v>
+      </c>
+      <c r="J39" t="s">
         <v>231</v>
       </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>21</v>
-      </c>
-      <c r="G39" t="s">
-        <v>174</v>
-      </c>
-      <c r="H39" t="s">
-        <v>175</v>
-      </c>
-      <c r="J39" t="s">
-        <v>230</v>
-      </c>
       <c r="K39" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L39">
         <v>24.160855221960116</v>
@@ -7189,31 +7194,31 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C40" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D40" t="s">
+        <v>234</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" t="s">
+        <v>175</v>
+      </c>
+      <c r="H40" t="s">
+        <v>176</v>
+      </c>
+      <c r="J40" t="s">
         <v>233</v>
       </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" t="s">
-        <v>21</v>
-      </c>
-      <c r="G40" t="s">
-        <v>174</v>
-      </c>
-      <c r="H40" t="s">
-        <v>175</v>
-      </c>
-      <c r="J40" t="s">
-        <v>232</v>
-      </c>
       <c r="K40" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L40">
         <v>15.135830259815824</v>
@@ -7224,31 +7229,31 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C41" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D41" t="s">
+        <v>236</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" t="s">
+        <v>175</v>
+      </c>
+      <c r="H41" t="s">
+        <v>176</v>
+      </c>
+      <c r="J41" t="s">
         <v>235</v>
       </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>21</v>
-      </c>
-      <c r="G41" t="s">
-        <v>174</v>
-      </c>
-      <c r="H41" t="s">
-        <v>175</v>
-      </c>
-      <c r="J41" t="s">
-        <v>234</v>
-      </c>
       <c r="K41" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L41">
         <v>42.775558022717121</v>
@@ -7259,31 +7264,31 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C42" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D42" t="s">
+        <v>238</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H42" t="s">
+        <v>176</v>
+      </c>
+      <c r="J42" t="s">
         <v>237</v>
       </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>21</v>
-      </c>
-      <c r="G42" t="s">
-        <v>174</v>
-      </c>
-      <c r="H42" t="s">
-        <v>175</v>
-      </c>
-      <c r="J42" t="s">
-        <v>236</v>
-      </c>
       <c r="K42" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L42">
         <v>37.425650341443877</v>
@@ -7294,31 +7299,31 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C43" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D43" t="s">
+        <v>240</v>
+      </c>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" t="s">
+        <v>175</v>
+      </c>
+      <c r="H43" t="s">
+        <v>176</v>
+      </c>
+      <c r="J43" t="s">
         <v>239</v>
       </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>21</v>
-      </c>
-      <c r="G43" t="s">
-        <v>174</v>
-      </c>
-      <c r="H43" t="s">
-        <v>175</v>
-      </c>
-      <c r="J43" t="s">
-        <v>238</v>
-      </c>
       <c r="K43" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L43">
         <v>16.943978704073047</v>
@@ -7329,31 +7334,31 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C44" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D44" t="s">
+        <v>242</v>
+      </c>
+      <c r="E44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" t="s">
+        <v>175</v>
+      </c>
+      <c r="H44" t="s">
+        <v>176</v>
+      </c>
+      <c r="J44" t="s">
         <v>241</v>
       </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>21</v>
-      </c>
-      <c r="G44" t="s">
-        <v>174</v>
-      </c>
-      <c r="H44" t="s">
-        <v>175</v>
-      </c>
-      <c r="J44" t="s">
-        <v>240</v>
-      </c>
       <c r="K44" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L44">
         <v>10.266928441851084</v>
@@ -7364,31 +7369,31 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C45" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D45" t="s">
+        <v>244</v>
+      </c>
+      <c r="E45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" t="s">
+        <v>175</v>
+      </c>
+      <c r="H45" t="s">
+        <v>176</v>
+      </c>
+      <c r="J45" t="s">
         <v>243</v>
       </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" t="s">
-        <v>21</v>
-      </c>
-      <c r="G45" t="s">
-        <v>174</v>
-      </c>
-      <c r="H45" t="s">
-        <v>175</v>
-      </c>
-      <c r="J45" t="s">
-        <v>242</v>
-      </c>
       <c r="K45" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L45">
         <v>16.976513673223863</v>
@@ -7399,31 +7404,31 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C46" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D46" t="s">
+        <v>246</v>
+      </c>
+      <c r="E46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" t="s">
+        <v>175</v>
+      </c>
+      <c r="H46" t="s">
+        <v>176</v>
+      </c>
+      <c r="J46" t="s">
         <v>245</v>
       </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>21</v>
-      </c>
-      <c r="G46" t="s">
-        <v>174</v>
-      </c>
-      <c r="H46" t="s">
-        <v>175</v>
-      </c>
-      <c r="J46" t="s">
-        <v>244</v>
-      </c>
       <c r="K46" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L46">
         <v>9.5580808778951578</v>
@@ -7438,119 +7443,119 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0637C431-8078-42E9-B36A-7CCC874CA641}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56E9863B-D0CA-418E-AFD1-5278BB994912}">
   <dimension ref="B9:Z37"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:26">
       <c r="B9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="W9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="2:26">
       <c r="B10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K10" t="s">
+        <v>248</v>
+      </c>
+      <c r="L10" t="s">
+        <v>249</v>
+      </c>
+      <c r="M10" t="s">
+        <v>250</v>
+      </c>
+      <c r="O10" t="s">
         <v>165</v>
       </c>
-      <c r="D10" t="s">
+      <c r="P10" t="s">
         <v>166</v>
       </c>
-      <c r="E10" t="s">
+      <c r="Q10" t="s">
         <v>167</v>
       </c>
-      <c r="F10" t="s">
+      <c r="R10" t="s">
         <v>168</v>
       </c>
-      <c r="G10" t="s">
+      <c r="S10" t="s">
         <v>169</v>
       </c>
-      <c r="H10" t="s">
+      <c r="T10" t="s">
         <v>170</v>
       </c>
-      <c r="J10" t="s">
-        <v>165</v>
-      </c>
-      <c r="K10" t="s">
-        <v>247</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="U10" t="s">
+        <v>171</v>
+      </c>
+      <c r="W10" t="s">
+        <v>166</v>
+      </c>
+      <c r="X10" t="s">
         <v>248</v>
       </c>
-      <c r="M10" t="s">
+      <c r="Y10" t="s">
         <v>249</v>
       </c>
-      <c r="O10" t="s">
-        <v>164</v>
-      </c>
-      <c r="P10" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>166</v>
-      </c>
-      <c r="R10" t="s">
-        <v>167</v>
-      </c>
-      <c r="S10" t="s">
-        <v>168</v>
-      </c>
-      <c r="T10" t="s">
-        <v>169</v>
-      </c>
-      <c r="U10" t="s">
-        <v>170</v>
-      </c>
-      <c r="W10" t="s">
-        <v>165</v>
-      </c>
-      <c r="X10" t="s">
-        <v>247</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>248</v>
-      </c>
       <c r="Z10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="2:26">
       <c r="B11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D11" t="s">
+        <v>288</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" t="s">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J11" t="s">
         <v>287</v>
       </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" t="s">
-        <v>174</v>
-      </c>
-      <c r="H11" t="s">
-        <v>175</v>
-      </c>
-      <c r="J11" t="s">
-        <v>286</v>
-      </c>
       <c r="K11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L11">
         <v>10.088237612202811</v>
@@ -7559,31 +7564,31 @@
         <v>0.1480664930336153</v>
       </c>
       <c r="O11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q11" t="s">
+        <v>369</v>
+      </c>
+      <c r="R11" t="s">
+        <v>10</v>
+      </c>
+      <c r="S11" t="s">
+        <v>21</v>
+      </c>
+      <c r="T11" t="s">
+        <v>175</v>
+      </c>
+      <c r="U11" t="s">
+        <v>176</v>
+      </c>
+      <c r="W11" t="s">
         <v>368</v>
       </c>
-      <c r="R11" t="s">
-        <v>10</v>
-      </c>
-      <c r="S11" t="s">
-        <v>21</v>
-      </c>
-      <c r="T11" t="s">
-        <v>174</v>
-      </c>
-      <c r="U11" t="s">
-        <v>175</v>
-      </c>
-      <c r="W11" t="s">
-        <v>367</v>
-      </c>
       <c r="X11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Y11">
         <v>0.16350000000000001</v>
@@ -7594,31 +7599,31 @@
     </row>
     <row r="12" spans="2:26">
       <c r="B12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D12" t="s">
+        <v>290</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" t="s">
+        <v>175</v>
+      </c>
+      <c r="H12" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" t="s">
         <v>289</v>
       </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" t="s">
-        <v>174</v>
-      </c>
-      <c r="H12" t="s">
-        <v>175</v>
-      </c>
-      <c r="J12" t="s">
-        <v>288</v>
-      </c>
       <c r="K12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L12">
         <v>4.7527038630847755</v>
@@ -7627,31 +7632,31 @@
         <v>0.1248854530556643</v>
       </c>
       <c r="O12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P12" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q12" t="s">
+        <v>371</v>
+      </c>
+      <c r="R12" t="s">
+        <v>10</v>
+      </c>
+      <c r="S12" t="s">
+        <v>21</v>
+      </c>
+      <c r="T12" t="s">
+        <v>175</v>
+      </c>
+      <c r="U12" t="s">
+        <v>176</v>
+      </c>
+      <c r="W12" t="s">
         <v>370</v>
       </c>
-      <c r="R12" t="s">
-        <v>10</v>
-      </c>
-      <c r="S12" t="s">
-        <v>21</v>
-      </c>
-      <c r="T12" t="s">
-        <v>174</v>
-      </c>
-      <c r="U12" t="s">
-        <v>175</v>
-      </c>
-      <c r="W12" t="s">
-        <v>369</v>
-      </c>
       <c r="X12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Y12">
         <v>13.40025</v>
@@ -7662,31 +7667,31 @@
     </row>
     <row r="13" spans="2:26">
       <c r="B13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D13" t="s">
+        <v>292</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>175</v>
+      </c>
+      <c r="H13" t="s">
+        <v>176</v>
+      </c>
+      <c r="J13" t="s">
         <v>291</v>
       </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" t="s">
-        <v>174</v>
-      </c>
-      <c r="H13" t="s">
-        <v>175</v>
-      </c>
-      <c r="J13" t="s">
-        <v>290</v>
-      </c>
       <c r="K13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L13">
         <v>1.4400913107240583</v>
@@ -7695,31 +7700,31 @@
         <v>9.9841122892969203E-2</v>
       </c>
       <c r="O13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q13" t="s">
+        <v>373</v>
+      </c>
+      <c r="R13" t="s">
+        <v>10</v>
+      </c>
+      <c r="S13" t="s">
+        <v>21</v>
+      </c>
+      <c r="T13" t="s">
+        <v>175</v>
+      </c>
+      <c r="U13" t="s">
+        <v>176</v>
+      </c>
+      <c r="W13" t="s">
         <v>372</v>
       </c>
-      <c r="R13" t="s">
-        <v>10</v>
-      </c>
-      <c r="S13" t="s">
-        <v>21</v>
-      </c>
-      <c r="T13" t="s">
-        <v>174</v>
-      </c>
-      <c r="U13" t="s">
-        <v>175</v>
-      </c>
-      <c r="W13" t="s">
-        <v>371</v>
-      </c>
       <c r="X13" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Y13">
         <v>8.4097500000000007</v>
@@ -7730,31 +7735,31 @@
     </row>
     <row r="14" spans="2:26">
       <c r="B14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D14" t="s">
+        <v>294</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" t="s">
+        <v>176</v>
+      </c>
+      <c r="J14" t="s">
         <v>293</v>
       </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" t="s">
-        <v>174</v>
-      </c>
-      <c r="H14" t="s">
-        <v>175</v>
-      </c>
-      <c r="J14" t="s">
-        <v>292</v>
-      </c>
       <c r="K14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L14">
         <v>1.437273477445641</v>
@@ -7763,31 +7768,31 @@
         <v>0.12675637508700771</v>
       </c>
       <c r="O14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q14" t="s">
+        <v>375</v>
+      </c>
+      <c r="R14" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" t="s">
+        <v>21</v>
+      </c>
+      <c r="T14" t="s">
+        <v>175</v>
+      </c>
+      <c r="U14" t="s">
+        <v>176</v>
+      </c>
+      <c r="W14" t="s">
         <v>374</v>
       </c>
-      <c r="R14" t="s">
-        <v>10</v>
-      </c>
-      <c r="S14" t="s">
-        <v>21</v>
-      </c>
-      <c r="T14" t="s">
-        <v>174</v>
-      </c>
-      <c r="U14" t="s">
-        <v>175</v>
-      </c>
-      <c r="W14" t="s">
-        <v>373</v>
-      </c>
       <c r="X14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Y14">
         <v>14.358750000000001</v>
@@ -7798,31 +7803,31 @@
     </row>
     <row r="15" spans="2:26">
       <c r="B15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D15" t="s">
+        <v>296</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>176</v>
+      </c>
+      <c r="J15" t="s">
         <v>295</v>
       </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" t="s">
-        <v>174</v>
-      </c>
-      <c r="H15" t="s">
-        <v>175</v>
-      </c>
-      <c r="J15" t="s">
-        <v>294</v>
-      </c>
       <c r="K15" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L15">
         <v>2.1922713563210485</v>
@@ -7831,31 +7836,31 @@
         <v>0.11693299272226811</v>
       </c>
       <c r="O15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P15" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q15" t="s">
+        <v>377</v>
+      </c>
+      <c r="R15" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" t="s">
+        <v>21</v>
+      </c>
+      <c r="T15" t="s">
+        <v>175</v>
+      </c>
+      <c r="U15" t="s">
+        <v>176</v>
+      </c>
+      <c r="W15" t="s">
         <v>376</v>
       </c>
-      <c r="R15" t="s">
-        <v>10</v>
-      </c>
-      <c r="S15" t="s">
-        <v>21</v>
-      </c>
-      <c r="T15" t="s">
-        <v>174</v>
-      </c>
-      <c r="U15" t="s">
-        <v>175</v>
-      </c>
-      <c r="W15" t="s">
-        <v>375</v>
-      </c>
       <c r="X15" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Y15">
         <v>12.78825</v>
@@ -7866,31 +7871,31 @@
     </row>
     <row r="16" spans="2:26">
       <c r="B16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D16" t="s">
+        <v>298</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H16" t="s">
+        <v>176</v>
+      </c>
+      <c r="J16" t="s">
         <v>297</v>
       </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" t="s">
-        <v>174</v>
-      </c>
-      <c r="H16" t="s">
-        <v>175</v>
-      </c>
-      <c r="J16" t="s">
-        <v>296</v>
-      </c>
       <c r="K16" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L16">
         <v>0.73811583011208182</v>
@@ -7899,31 +7904,31 @@
         <v>9.8225724600873393E-2</v>
       </c>
       <c r="O16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q16" t="s">
+        <v>379</v>
+      </c>
+      <c r="R16" t="s">
+        <v>10</v>
+      </c>
+      <c r="S16" t="s">
+        <v>21</v>
+      </c>
+      <c r="T16" t="s">
+        <v>175</v>
+      </c>
+      <c r="U16" t="s">
+        <v>176</v>
+      </c>
+      <c r="W16" t="s">
         <v>378</v>
       </c>
-      <c r="R16" t="s">
-        <v>10</v>
-      </c>
-      <c r="S16" t="s">
-        <v>21</v>
-      </c>
-      <c r="T16" t="s">
-        <v>174</v>
-      </c>
-      <c r="U16" t="s">
-        <v>175</v>
-      </c>
-      <c r="W16" t="s">
-        <v>377</v>
-      </c>
       <c r="X16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Y16">
         <v>24.802499999999998</v>
@@ -7934,31 +7939,31 @@
     </row>
     <row r="17" spans="2:26">
       <c r="B17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D17" t="s">
+        <v>300</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>176</v>
+      </c>
+      <c r="J17" t="s">
         <v>299</v>
       </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" t="s">
-        <v>174</v>
-      </c>
-      <c r="H17" t="s">
-        <v>175</v>
-      </c>
-      <c r="J17" t="s">
-        <v>298</v>
-      </c>
       <c r="K17" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L17">
         <v>5.5236145427785717</v>
@@ -7967,31 +7972,31 @@
         <v>9.8218117716251802E-2</v>
       </c>
       <c r="O17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P17" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q17" t="s">
+        <v>381</v>
+      </c>
+      <c r="R17" t="s">
+        <v>10</v>
+      </c>
+      <c r="S17" t="s">
+        <v>21</v>
+      </c>
+      <c r="T17" t="s">
+        <v>175</v>
+      </c>
+      <c r="U17" t="s">
+        <v>176</v>
+      </c>
+      <c r="W17" t="s">
         <v>380</v>
       </c>
-      <c r="R17" t="s">
-        <v>10</v>
-      </c>
-      <c r="S17" t="s">
-        <v>21</v>
-      </c>
-      <c r="T17" t="s">
-        <v>174</v>
-      </c>
-      <c r="U17" t="s">
-        <v>175</v>
-      </c>
-      <c r="W17" t="s">
-        <v>379</v>
-      </c>
       <c r="X17" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Y17">
         <v>8.6609999999999996</v>
@@ -8002,31 +8007,31 @@
     </row>
     <row r="18" spans="2:26">
       <c r="B18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D18" t="s">
+        <v>302</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" t="s">
+        <v>175</v>
+      </c>
+      <c r="H18" t="s">
+        <v>176</v>
+      </c>
+      <c r="J18" t="s">
         <v>301</v>
       </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" t="s">
-        <v>174</v>
-      </c>
-      <c r="H18" t="s">
-        <v>175</v>
-      </c>
-      <c r="J18" t="s">
-        <v>300</v>
-      </c>
       <c r="K18" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L18">
         <v>5.5488357050452785E-3</v>
@@ -8035,31 +8040,31 @@
         <v>0.15003138728880019</v>
       </c>
       <c r="O18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q18" t="s">
+        <v>383</v>
+      </c>
+      <c r="R18" t="s">
+        <v>10</v>
+      </c>
+      <c r="S18" t="s">
+        <v>21</v>
+      </c>
+      <c r="T18" t="s">
+        <v>175</v>
+      </c>
+      <c r="U18" t="s">
+        <v>176</v>
+      </c>
+      <c r="W18" t="s">
         <v>382</v>
       </c>
-      <c r="R18" t="s">
-        <v>10</v>
-      </c>
-      <c r="S18" t="s">
-        <v>21</v>
-      </c>
-      <c r="T18" t="s">
-        <v>174</v>
-      </c>
-      <c r="U18" t="s">
-        <v>175</v>
-      </c>
-      <c r="W18" t="s">
-        <v>381</v>
-      </c>
       <c r="X18" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Y18">
         <v>3.4147500000000002</v>
@@ -8070,31 +8075,31 @@
     </row>
     <row r="19" spans="2:26">
       <c r="B19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D19" t="s">
+        <v>304</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>176</v>
+      </c>
+      <c r="J19" t="s">
         <v>303</v>
       </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" t="s">
-        <v>174</v>
-      </c>
-      <c r="H19" t="s">
-        <v>175</v>
-      </c>
-      <c r="J19" t="s">
-        <v>302</v>
-      </c>
       <c r="K19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L19">
         <v>6.6811161360847313</v>
@@ -8103,31 +8108,31 @@
         <v>0.10894863026132159</v>
       </c>
       <c r="O19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P19" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q19" t="s">
+        <v>385</v>
+      </c>
+      <c r="R19" t="s">
+        <v>10</v>
+      </c>
+      <c r="S19" t="s">
+        <v>21</v>
+      </c>
+      <c r="T19" t="s">
+        <v>175</v>
+      </c>
+      <c r="U19" t="s">
+        <v>176</v>
+      </c>
+      <c r="W19" t="s">
         <v>384</v>
       </c>
-      <c r="R19" t="s">
-        <v>10</v>
-      </c>
-      <c r="S19" t="s">
-        <v>21</v>
-      </c>
-      <c r="T19" t="s">
-        <v>174</v>
-      </c>
-      <c r="U19" t="s">
-        <v>175</v>
-      </c>
-      <c r="W19" t="s">
-        <v>383</v>
-      </c>
       <c r="X19" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Y19">
         <v>1.7250000000000001E-2</v>
@@ -8138,31 +8143,31 @@
     </row>
     <row r="20" spans="2:26">
       <c r="B20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D20" t="s">
+        <v>306</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" t="s">
+        <v>175</v>
+      </c>
+      <c r="H20" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" t="s">
         <v>305</v>
       </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" t="s">
-        <v>174</v>
-      </c>
-      <c r="H20" t="s">
-        <v>175</v>
-      </c>
-      <c r="J20" t="s">
-        <v>304</v>
-      </c>
       <c r="K20" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L20">
         <v>18.094012332227912</v>
@@ -8171,31 +8176,31 @@
         <v>0.13703415293889221</v>
       </c>
       <c r="O20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P20" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q20" t="s">
+        <v>387</v>
+      </c>
+      <c r="R20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S20" t="s">
+        <v>21</v>
+      </c>
+      <c r="T20" t="s">
+        <v>175</v>
+      </c>
+      <c r="U20" t="s">
+        <v>176</v>
+      </c>
+      <c r="W20" t="s">
         <v>386</v>
       </c>
-      <c r="R20" t="s">
-        <v>10</v>
-      </c>
-      <c r="S20" t="s">
-        <v>21</v>
-      </c>
-      <c r="T20" t="s">
-        <v>174</v>
-      </c>
-      <c r="U20" t="s">
-        <v>175</v>
-      </c>
-      <c r="W20" t="s">
-        <v>385</v>
-      </c>
       <c r="X20" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Y20">
         <v>6.8624999999999998</v>
@@ -8206,31 +8211,31 @@
     </row>
     <row r="21" spans="2:26">
       <c r="B21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D21" t="s">
+        <v>308</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" t="s">
+        <v>175</v>
+      </c>
+      <c r="H21" t="s">
+        <v>176</v>
+      </c>
+      <c r="J21" t="s">
         <v>307</v>
       </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" t="s">
-        <v>174</v>
-      </c>
-      <c r="H21" t="s">
-        <v>175</v>
-      </c>
-      <c r="J21" t="s">
-        <v>306</v>
-      </c>
       <c r="K21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L21">
         <v>1.3529085560597105</v>
@@ -8241,31 +8246,31 @@
     </row>
     <row r="22" spans="2:26">
       <c r="B22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D22" t="s">
+        <v>310</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" t="s">
+        <v>175</v>
+      </c>
+      <c r="H22" t="s">
+        <v>176</v>
+      </c>
+      <c r="J22" t="s">
         <v>309</v>
       </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" t="s">
-        <v>174</v>
-      </c>
-      <c r="H22" t="s">
-        <v>175</v>
-      </c>
-      <c r="J22" t="s">
-        <v>308</v>
-      </c>
       <c r="K22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L22">
         <v>3.7088360788644938</v>
@@ -8276,31 +8281,31 @@
     </row>
     <row r="23" spans="2:26">
       <c r="B23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D23" t="s">
+        <v>312</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" t="s">
+        <v>176</v>
+      </c>
+      <c r="J23" t="s">
         <v>311</v>
       </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" t="s">
-        <v>174</v>
-      </c>
-      <c r="H23" t="s">
-        <v>175</v>
-      </c>
-      <c r="J23" t="s">
-        <v>310</v>
-      </c>
       <c r="K23" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L23">
         <v>13.683903390107789</v>
@@ -8311,31 +8316,31 @@
     </row>
     <row r="24" spans="2:26">
       <c r="B24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D24" t="s">
+        <v>314</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" t="s">
+        <v>175</v>
+      </c>
+      <c r="H24" t="s">
+        <v>176</v>
+      </c>
+      <c r="J24" t="s">
         <v>313</v>
       </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" t="s">
-        <v>174</v>
-      </c>
-      <c r="H24" t="s">
-        <v>175</v>
-      </c>
-      <c r="J24" t="s">
-        <v>312</v>
-      </c>
       <c r="K24" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L24">
         <v>5.4676081362262012</v>
@@ -8346,31 +8351,31 @@
     </row>
     <row r="25" spans="2:26">
       <c r="B25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D25" t="s">
+        <v>316</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>175</v>
+      </c>
+      <c r="H25" t="s">
+        <v>176</v>
+      </c>
+      <c r="J25" t="s">
         <v>315</v>
       </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" t="s">
-        <v>174</v>
-      </c>
-      <c r="H25" t="s">
-        <v>175</v>
-      </c>
-      <c r="J25" t="s">
-        <v>314</v>
-      </c>
       <c r="K25" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L25">
         <v>8.9064794695455216</v>
@@ -8381,31 +8386,31 @@
     </row>
     <row r="26" spans="2:26">
       <c r="B26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D26" t="s">
+        <v>318</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>175</v>
+      </c>
+      <c r="H26" t="s">
+        <v>176</v>
+      </c>
+      <c r="J26" t="s">
         <v>317</v>
       </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" t="s">
-        <v>174</v>
-      </c>
-      <c r="H26" t="s">
-        <v>175</v>
-      </c>
-      <c r="J26" t="s">
-        <v>316</v>
-      </c>
       <c r="K26" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L26">
         <v>14.189229081738485</v>
@@ -8416,31 +8421,31 @@
     </row>
     <row r="27" spans="2:26">
       <c r="B27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D27" t="s">
+        <v>320</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" t="s">
+        <v>175</v>
+      </c>
+      <c r="H27" t="s">
+        <v>176</v>
+      </c>
+      <c r="J27" t="s">
         <v>319</v>
       </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" t="s">
-        <v>174</v>
-      </c>
-      <c r="H27" t="s">
-        <v>175</v>
-      </c>
-      <c r="J27" t="s">
-        <v>318</v>
-      </c>
       <c r="K27" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L27">
         <v>10.717982842540293</v>
@@ -8451,31 +8456,31 @@
     </row>
     <row r="28" spans="2:26">
       <c r="B28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D28" t="s">
+        <v>322</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>175</v>
+      </c>
+      <c r="H28" t="s">
+        <v>176</v>
+      </c>
+      <c r="J28" t="s">
         <v>321</v>
       </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" t="s">
-        <v>174</v>
-      </c>
-      <c r="H28" t="s">
-        <v>175</v>
-      </c>
-      <c r="J28" t="s">
-        <v>320</v>
-      </c>
       <c r="K28" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L28">
         <v>9.6743476082482847</v>
@@ -8486,31 +8491,31 @@
     </row>
     <row r="29" spans="2:26">
       <c r="B29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D29" t="s">
+        <v>324</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" t="s">
+        <v>175</v>
+      </c>
+      <c r="H29" t="s">
+        <v>176</v>
+      </c>
+      <c r="J29" t="s">
         <v>323</v>
       </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" t="s">
-        <v>174</v>
-      </c>
-      <c r="H29" t="s">
-        <v>175</v>
-      </c>
-      <c r="J29" t="s">
-        <v>322</v>
-      </c>
       <c r="K29" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L29">
         <v>23.206762484053751</v>
@@ -8521,31 +8526,31 @@
     </row>
     <row r="30" spans="2:26">
       <c r="B30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D30" t="s">
+        <v>326</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" t="s">
+        <v>175</v>
+      </c>
+      <c r="H30" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" t="s">
         <v>325</v>
       </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" t="s">
-        <v>174</v>
-      </c>
-      <c r="H30" t="s">
-        <v>175</v>
-      </c>
-      <c r="J30" t="s">
-        <v>324</v>
-      </c>
       <c r="K30" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L30">
         <v>5.8372174437039801</v>
@@ -8556,31 +8561,31 @@
     </row>
     <row r="31" spans="2:26">
       <c r="B31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D31" t="s">
+        <v>328</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" t="s">
+        <v>175</v>
+      </c>
+      <c r="H31" t="s">
+        <v>176</v>
+      </c>
+      <c r="J31" t="s">
         <v>327</v>
       </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" t="s">
-        <v>174</v>
-      </c>
-      <c r="H31" t="s">
-        <v>175</v>
-      </c>
-      <c r="J31" t="s">
-        <v>326</v>
-      </c>
       <c r="K31" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L31">
         <v>1.8845590125315521</v>
@@ -8591,31 +8596,31 @@
     </row>
     <row r="32" spans="2:26">
       <c r="B32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D32" t="s">
+        <v>330</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" t="s">
+        <v>176</v>
+      </c>
+      <c r="J32" t="s">
         <v>329</v>
       </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" t="s">
-        <v>174</v>
-      </c>
-      <c r="H32" t="s">
-        <v>175</v>
-      </c>
-      <c r="J32" t="s">
-        <v>328</v>
-      </c>
       <c r="K32" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L32">
         <v>7.179650801796102</v>
@@ -8626,31 +8631,31 @@
     </row>
     <row r="33" spans="2:13">
       <c r="B33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C33" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D33" t="s">
+        <v>332</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" t="s">
+        <v>175</v>
+      </c>
+      <c r="H33" t="s">
+        <v>176</v>
+      </c>
+      <c r="J33" t="s">
         <v>331</v>
       </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" t="s">
-        <v>174</v>
-      </c>
-      <c r="H33" t="s">
-        <v>175</v>
-      </c>
-      <c r="J33" t="s">
-        <v>330</v>
-      </c>
       <c r="K33" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L33">
         <v>14.559476964149322</v>
@@ -8661,31 +8666,31 @@
     </row>
     <row r="34" spans="2:13">
       <c r="B34" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C34" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D34" t="s">
+        <v>334</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" t="s">
+        <v>175</v>
+      </c>
+      <c r="H34" t="s">
+        <v>176</v>
+      </c>
+      <c r="J34" t="s">
         <v>333</v>
       </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" t="s">
-        <v>174</v>
-      </c>
-      <c r="H34" t="s">
-        <v>175</v>
-      </c>
-      <c r="J34" t="s">
-        <v>332</v>
-      </c>
       <c r="K34" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L34">
         <v>1.3536151515148049</v>
@@ -8696,31 +8701,31 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C35" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D35" t="s">
+        <v>336</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" t="s">
+        <v>175</v>
+      </c>
+      <c r="H35" t="s">
+        <v>176</v>
+      </c>
+      <c r="J35" t="s">
         <v>335</v>
       </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" t="s">
-        <v>174</v>
-      </c>
-      <c r="H35" t="s">
-        <v>175</v>
-      </c>
-      <c r="J35" t="s">
-        <v>334</v>
-      </c>
       <c r="K35" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L35">
         <v>4.820514286595051</v>
@@ -8731,31 +8736,31 @@
     </row>
     <row r="36" spans="2:13">
       <c r="B36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C36" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D36" t="s">
+        <v>338</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" t="s">
+        <v>175</v>
+      </c>
+      <c r="H36" t="s">
+        <v>176</v>
+      </c>
+      <c r="J36" t="s">
         <v>337</v>
       </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36" t="s">
-        <v>174</v>
-      </c>
-      <c r="H36" t="s">
-        <v>175</v>
-      </c>
-      <c r="J36" t="s">
-        <v>336</v>
-      </c>
       <c r="K36" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L36">
         <v>8.1474073379531564</v>
@@ -8766,31 +8771,31 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C37" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D37" t="s">
+        <v>340</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" t="s">
+        <v>175</v>
+      </c>
+      <c r="H37" t="s">
+        <v>176</v>
+      </c>
+      <c r="J37" t="s">
         <v>339</v>
       </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37" t="s">
-        <v>174</v>
-      </c>
-      <c r="H37" t="s">
-        <v>175</v>
-      </c>
-      <c r="J37" t="s">
-        <v>338</v>
-      </c>
       <c r="K37" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L37">
         <v>9.9689850956014183</v>
@@ -8805,27 +8810,27 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4577C4-C0F8-4785-8E09-41145986F7A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BD49A9-B7AE-4446-A97A-09E413D04A0F}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:16">
       <c r="B9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="B10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E10">
         <v>2023</v>
@@ -8840,30 +8845,30 @@
         <v>54</v>
       </c>
       <c r="J10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -8884,10 +8889,10 @@
         <v>146</v>
       </c>
       <c r="J11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -8896,15 +8901,15 @@
         <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -8922,13 +8927,13 @@
         <v>0.5</v>
       </c>
       <c r="H12" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K12" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -8937,15 +8942,15 @@
         <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -8963,13 +8968,13 @@
         <v>4400</v>
       </c>
       <c r="H13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -8978,15 +8983,15 @@
         <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P13" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -9004,13 +9009,13 @@
         <v>155</v>
       </c>
       <c r="H14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -9019,15 +9024,15 @@
         <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -9045,13 +9050,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K15" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -9060,15 +9065,15 @@
         <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P15" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -9089,10 +9094,10 @@
         <v>146</v>
       </c>
       <c r="J16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K16" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -9101,15 +9106,15 @@
         <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P16" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -9127,13 +9132,13 @@
         <v>0.5</v>
       </c>
       <c r="H17" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K17" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -9142,15 +9147,15 @@
         <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P17" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -9168,13 +9173,13 @@
         <v>2050</v>
       </c>
       <c r="H18" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K18" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -9183,15 +9188,15 @@
         <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -9209,13 +9214,13 @@
         <v>70</v>
       </c>
       <c r="H19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K19" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -9224,15 +9229,15 @@
         <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P19" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -9250,13 +9255,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K20" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -9265,15 +9270,15 @@
         <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P20" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -9294,10 +9299,10 @@
         <v>146</v>
       </c>
       <c r="J21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K21" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -9306,15 +9311,15 @@
         <v>21</v>
       </c>
       <c r="O21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -9332,13 +9337,13 @@
         <v>700</v>
       </c>
       <c r="H22" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K22" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -9347,15 +9352,15 @@
         <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P22" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -9373,13 +9378,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K23" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -9388,15 +9393,15 @@
         <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P23" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -9417,10 +9422,10 @@
         <v>146</v>
       </c>
       <c r="J24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K24" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -9429,15 +9434,15 @@
         <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P24" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -9455,13 +9460,13 @@
         <v>1850</v>
       </c>
       <c r="H25" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K25" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -9470,15 +9475,15 @@
         <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P25" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -9496,13 +9501,13 @@
         <v>65</v>
       </c>
       <c r="H26" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K26" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -9511,15 +9516,15 @@
         <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P26" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -9540,10 +9545,10 @@
         <v>146</v>
       </c>
       <c r="J27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K27" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -9552,15 +9557,15 @@
         <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P27" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -9578,12 +9583,12 @@
         <v>3550</v>
       </c>
       <c r="H28" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -9601,12 +9606,12 @@
         <v>135</v>
       </c>
       <c r="H29" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -9629,7 +9634,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -9647,12 +9652,12 @@
         <v>400</v>
       </c>
       <c r="H31" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -9670,12 +9675,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -9698,7 +9703,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -9716,12 +9721,12 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -9739,12 +9744,12 @@
         <v>2100</v>
       </c>
       <c r="H35" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -9762,12 +9767,12 @@
         <v>50</v>
       </c>
       <c r="H36" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -9785,12 +9790,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -9813,7 +9818,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -9831,12 +9836,12 @@
         <v>2100</v>
       </c>
       <c r="H39" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -9854,12 +9859,12 @@
         <v>85</v>
       </c>
       <c r="H40" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -9882,7 +9887,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -9900,12 +9905,12 @@
         <v>4200</v>
       </c>
       <c r="H42" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -9923,12 +9928,12 @@
         <v>190</v>
       </c>
       <c r="H43" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -9951,7 +9956,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -9969,12 +9974,12 @@
         <v>4000</v>
       </c>
       <c r="H45" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -9992,12 +9997,12 @@
         <v>170</v>
       </c>
       <c r="H46" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -10020,7 +10025,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -10038,12 +10043,12 @@
         <v>4300</v>
       </c>
       <c r="H48" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -10061,12 +10066,12 @@
         <v>165</v>
       </c>
       <c r="H49" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -10089,7 +10094,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -10107,12 +10112,12 @@
         <v>0.23</v>
       </c>
       <c r="H51" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -10130,12 +10135,12 @@
         <v>550</v>
       </c>
       <c r="H52" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -10153,12 +10158,12 @@
         <v>18</v>
       </c>
       <c r="H53" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -10176,12 +10181,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -10204,7 +10209,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -10222,12 +10227,12 @@
         <v>1300</v>
       </c>
       <c r="H56" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -10245,12 +10250,12 @@
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -10273,7 +10278,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -10291,12 +10296,12 @@
         <v>1600</v>
       </c>
       <c r="H59" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -10314,12 +10319,12 @@
         <v>55</v>
       </c>
       <c r="H60" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -10342,7 +10347,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -10360,12 +10365,12 @@
         <v>1900</v>
       </c>
       <c r="H62" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -10383,15 +10388,15 @@
         <v>70</v>
       </c>
       <c r="H63" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C64" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -10411,10 +10416,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C65" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -10429,15 +10434,15 @@
         <v>0.43</v>
       </c>
       <c r="H65" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C66" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -10452,15 +10457,15 @@
         <v>2200</v>
       </c>
       <c r="H66" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C67" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -10475,15 +10480,15 @@
         <v>65</v>
       </c>
       <c r="H67" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C68" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -10498,15 +10503,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
+        <v>420</v>
+      </c>
+      <c r="C69" t="s">
         <v>419</v>
-      </c>
-      <c r="C69" t="s">
-        <v>418</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -10526,10 +10531,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
+        <v>420</v>
+      </c>
+      <c r="C70" t="s">
         <v>419</v>
-      </c>
-      <c r="C70" t="s">
-        <v>418</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -10544,15 +10549,15 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H70" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
+        <v>420</v>
+      </c>
+      <c r="C71" t="s">
         <v>419</v>
-      </c>
-      <c r="C71" t="s">
-        <v>418</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -10567,15 +10572,15 @@
         <v>1470</v>
       </c>
       <c r="H71" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
+        <v>420</v>
+      </c>
+      <c r="C72" t="s">
         <v>419</v>
-      </c>
-      <c r="C72" t="s">
-        <v>418</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -10590,15 +10595,15 @@
         <v>38</v>
       </c>
       <c r="H72" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
+        <v>420</v>
+      </c>
+      <c r="C73" t="s">
         <v>419</v>
-      </c>
-      <c r="C73" t="s">
-        <v>418</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -10613,7 +10618,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
